--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/108.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/108.xlsx
@@ -426,13 +426,13 @@
         <v>2.896770622501112</v>
       </c>
       <c r="E2">
-        <v>-27.59477016000979</v>
+        <v>-28.80132318919146</v>
       </c>
       <c r="F2">
-        <v>-3.696493591621577</v>
+        <v>-3.674194769505617</v>
       </c>
       <c r="G2">
-        <v>-16.27290995113568</v>
+        <v>-17.03836270381658</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>2.761375446099119</v>
       </c>
       <c r="E3">
-        <v>-27.70873373688682</v>
+        <v>-28.70866608252052</v>
       </c>
       <c r="F3">
-        <v>-3.550299170538506</v>
+        <v>-3.603200369616088</v>
       </c>
       <c r="G3">
-        <v>-16.44801629161712</v>
+        <v>-17.34787388264689</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>2.635561193436078</v>
       </c>
       <c r="E4">
-        <v>-27.50253872989557</v>
+        <v>-29.02437317643926</v>
       </c>
       <c r="F4">
-        <v>-3.562703972395429</v>
+        <v>-3.632203169122904</v>
       </c>
       <c r="G4">
-        <v>-15.96700230112487</v>
+        <v>-17.0017828308804</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>2.548362410740955</v>
       </c>
       <c r="E5">
-        <v>-28.25969052703004</v>
+        <v>-30.00441646423127</v>
       </c>
       <c r="F5">
-        <v>-3.553586132392815</v>
+        <v>-3.554175929983608</v>
       </c>
       <c r="G5">
-        <v>-16.3156474387749</v>
+        <v>-16.99121391424628</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>2.51405745570268</v>
       </c>
       <c r="E6">
-        <v>-28.48042646405992</v>
+        <v>-29.23650048438056</v>
       </c>
       <c r="F6">
-        <v>-3.571127640514497</v>
+        <v>-3.646482566412362</v>
       </c>
       <c r="G6">
-        <v>-15.66556554286484</v>
+        <v>-16.67093353077671</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>2.550834575753282</v>
       </c>
       <c r="E7">
-        <v>-28.89311988580095</v>
+        <v>-30.5338969663931</v>
       </c>
       <c r="F7">
-        <v>-3.607477230516742</v>
+        <v>-3.707724596868732</v>
       </c>
       <c r="G7">
-        <v>-15.33853826758624</v>
+        <v>-16.78703270756619</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>2.677221271608935</v>
       </c>
       <c r="E8">
-        <v>-28.92643134060137</v>
+        <v>-30.42512075649186</v>
       </c>
       <c r="F8">
-        <v>-3.499782841213584</v>
+        <v>-3.390165811168528</v>
       </c>
       <c r="G8">
-        <v>-15.43065916303477</v>
+        <v>-16.36230461233262</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>2.902233915138582</v>
       </c>
       <c r="E9">
-        <v>-29.83953472561199</v>
+        <v>-31.39488440828645</v>
       </c>
       <c r="F9">
-        <v>-3.454566406531773</v>
+        <v>-3.478068018116597</v>
       </c>
       <c r="G9">
-        <v>-15.18168627520834</v>
+        <v>-16.40781137131544</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>3.237125083974149</v>
       </c>
       <c r="E10">
-        <v>-29.87899584811483</v>
+        <v>-31.75079529444529</v>
       </c>
       <c r="F10">
-        <v>-3.497536308817192</v>
+        <v>-3.378701206313783</v>
       </c>
       <c r="G10">
-        <v>-14.89992243381543</v>
+        <v>-16.09534222004579</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>3.682139534053475</v>
       </c>
       <c r="E11">
-        <v>-30.57530306848224</v>
+        <v>-32.13389513854619</v>
       </c>
       <c r="F11">
-        <v>-3.39856711336772</v>
+        <v>-3.433134885086544</v>
       </c>
       <c r="G11">
-        <v>-14.67729817793606</v>
+        <v>-15.64474221142282</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>4.223654422334867</v>
       </c>
       <c r="E12">
-        <v>-30.6447698597599</v>
+        <v>-32.84139221818656</v>
       </c>
       <c r="F12">
-        <v>-3.364232112889084</v>
+        <v>-3.423247491766729</v>
       </c>
       <c r="G12">
-        <v>-14.51291138391078</v>
+        <v>-15.54297935209116</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>4.844186197953346</v>
       </c>
       <c r="E13">
-        <v>-31.51704452311736</v>
+        <v>-32.90085108190726</v>
       </c>
       <c r="F13">
-        <v>-3.372971388988619</v>
+        <v>-3.332080688884226</v>
       </c>
       <c r="G13">
-        <v>-14.48380672280228</v>
+        <v>-15.2516132733616</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>5.510710387303049</v>
       </c>
       <c r="E14">
-        <v>-32.09538952405897</v>
+        <v>-33.13754988981419</v>
       </c>
       <c r="F14">
-        <v>-3.150828930947278</v>
+        <v>-3.357656532445661</v>
       </c>
       <c r="G14">
-        <v>-13.91500865151794</v>
+        <v>-15.1167085426363</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>6.186465598143497</v>
       </c>
       <c r="E15">
-        <v>-32.93524937046953</v>
+        <v>-34.24462593046936</v>
       </c>
       <c r="F15">
-        <v>-2.99593582376741</v>
+        <v>-3.02703770627292</v>
       </c>
       <c r="G15">
-        <v>-13.58107061242612</v>
+        <v>-14.51245618389913</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>6.835861888274573</v>
       </c>
       <c r="E16">
-        <v>-32.97942463441435</v>
+        <v>-34.39683020610416</v>
       </c>
       <c r="F16">
-        <v>-2.891467097130753</v>
+        <v>-3.018954497156402</v>
       </c>
       <c r="G16">
-        <v>-13.45743166817095</v>
+        <v>-14.07997148046705</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>7.418356945194159</v>
       </c>
       <c r="E17">
-        <v>-34.03929812625057</v>
+        <v>-35.24930411686309</v>
       </c>
       <c r="F17">
-        <v>-2.830343523212983</v>
+        <v>-3.06935982524935</v>
       </c>
       <c r="G17">
-        <v>-12.95587408733475</v>
+        <v>-14.05239298085216</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>7.911013147284756</v>
       </c>
       <c r="E18">
-        <v>-34.74409170690836</v>
+        <v>-35.5192351312753</v>
       </c>
       <c r="F18">
-        <v>-2.600162587894876</v>
+        <v>-2.884292607055106</v>
       </c>
       <c r="G18">
-        <v>-12.74143018948292</v>
+        <v>-13.42457450369369</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>8.297375542155924</v>
       </c>
       <c r="E19">
-        <v>-35.23934373828322</v>
+        <v>-36.54581754644413</v>
       </c>
       <c r="F19">
-        <v>-2.569317499284233</v>
+        <v>-2.81004686510959</v>
       </c>
       <c r="G19">
-        <v>-12.79675933708076</v>
+        <v>-13.30630195375769</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>8.568580206858753</v>
       </c>
       <c r="E20">
-        <v>-35.53113143249345</v>
+        <v>-37.37128137398431</v>
       </c>
       <c r="F20">
-        <v>-2.372909931345665</v>
+        <v>-2.423026987582438</v>
       </c>
       <c r="G20">
-        <v>-12.5006177964108</v>
+        <v>-13.22958668197615</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>8.730879275253747</v>
       </c>
       <c r="E21">
-        <v>-36.67761651820037</v>
+        <v>-37.52672350853459</v>
       </c>
       <c r="F21">
-        <v>-2.359271690425974</v>
+        <v>-2.587134853751048</v>
       </c>
       <c r="G21">
-        <v>-12.62663702290869</v>
+        <v>-12.9447672070505</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>8.794010530463297</v>
       </c>
       <c r="E22">
-        <v>-36.83358621997255</v>
+        <v>-38.09220311482041</v>
       </c>
       <c r="F22">
-        <v>-2.174000693850642</v>
+        <v>-2.274733483500673</v>
       </c>
       <c r="G22">
-        <v>-12.43974679558022</v>
+        <v>-12.92700613023231</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>8.772811877732888</v>
       </c>
       <c r="E23">
-        <v>-37.01548369967566</v>
+        <v>-38.94775412366754</v>
       </c>
       <c r="F23">
-        <v>-1.944740074717046</v>
+        <v>-2.38256952362971</v>
       </c>
       <c r="G23">
-        <v>-12.3118206948517</v>
+        <v>-12.9420194542529</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>8.686998714727688</v>
       </c>
       <c r="E24">
-        <v>-37.37273954261477</v>
+        <v>-38.80568683709891</v>
       </c>
       <c r="F24">
-        <v>-1.967148241330175</v>
+        <v>-2.055058731952272</v>
       </c>
       <c r="G24">
-        <v>-12.38146795190689</v>
+        <v>-12.61167997816227</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>8.550268413056374</v>
       </c>
       <c r="E25">
-        <v>-37.94679834290812</v>
+        <v>-38.81068400816638</v>
       </c>
       <c r="F25">
-        <v>-1.818631906417057</v>
+        <v>-1.980208281802712</v>
       </c>
       <c r="G25">
-        <v>-12.09771778319042</v>
+        <v>-13.18702961906882</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>8.377121401459863</v>
       </c>
       <c r="E26">
-        <v>-38.14626630176098</v>
+        <v>-38.98984628956885</v>
       </c>
       <c r="F26">
-        <v>-1.818276536801256</v>
+        <v>-2.017066489390276</v>
       </c>
       <c r="G26">
-        <v>-12.2925665619953</v>
+        <v>-12.86604243412663</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>8.180850565096803</v>
       </c>
       <c r="E27">
-        <v>-38.06077550520718</v>
+        <v>-39.05179807823077</v>
       </c>
       <c r="F27">
-        <v>-1.779769878082121</v>
+        <v>-2.062716988591154</v>
       </c>
       <c r="G27">
-        <v>-12.06879023626826</v>
+        <v>-12.83722082466173</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>7.966305391246139</v>
       </c>
       <c r="E28">
-        <v>-37.7403859691645</v>
+        <v>-38.98119011150318</v>
       </c>
       <c r="F28">
-        <v>-1.737563730542083</v>
+        <v>-1.921988135631754</v>
       </c>
       <c r="G28">
-        <v>-12.37907773802753</v>
+        <v>-13.28038038218519</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>7.735020346377885</v>
       </c>
       <c r="E29">
-        <v>-37.8732853601046</v>
+        <v>-39.11462386237619</v>
       </c>
       <c r="F29">
-        <v>-1.612603679462375</v>
+        <v>-2.008760449442405</v>
       </c>
       <c r="G29">
-        <v>-12.30536513105012</v>
+        <v>-12.84405710120033</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>7.490602501696222</v>
       </c>
       <c r="E30">
-        <v>-37.66221545084409</v>
+        <v>-38.94962211919571</v>
       </c>
       <c r="F30">
-        <v>-1.546108971304853</v>
+        <v>-1.849952477916907</v>
       </c>
       <c r="G30">
-        <v>-12.34185065343843</v>
+        <v>-12.80779669590869</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>7.227380829777469</v>
       </c>
       <c r="E31">
-        <v>-37.32071869745167</v>
+        <v>-38.95682918557892</v>
       </c>
       <c r="F31">
-        <v>-1.639247288606019</v>
+        <v>-1.850522394690032</v>
       </c>
       <c r="G31">
-        <v>-12.25187995731766</v>
+        <v>-13.15148098106813</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>6.943077846238047</v>
       </c>
       <c r="E32">
-        <v>-36.757688995604</v>
+        <v>-38.57052318188059</v>
       </c>
       <c r="F32">
-        <v>-1.801829302018672</v>
+        <v>-2.002444976363462</v>
       </c>
       <c r="G32">
-        <v>-12.62926890661242</v>
+        <v>-13.26589674545088</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>6.634529461294209</v>
       </c>
       <c r="E33">
-        <v>-37.19762118850116</v>
+        <v>-38.15192689427057</v>
       </c>
       <c r="F33">
-        <v>-1.756688248770516</v>
+        <v>-2.06572810410033</v>
       </c>
       <c r="G33">
-        <v>-12.47505045321101</v>
+        <v>-13.10737127230288</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>6.294390361343299</v>
       </c>
       <c r="E34">
-        <v>-36.63374692625106</v>
+        <v>-38.07873090464759</v>
       </c>
       <c r="F34">
-        <v>-1.743108821936423</v>
+        <v>-1.861040175603378</v>
       </c>
       <c r="G34">
-        <v>-13.11975602316529</v>
+        <v>-13.6930316072915</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>5.925634380366098</v>
       </c>
       <c r="E35">
-        <v>-35.8413522801519</v>
+        <v>-37.75745831617342</v>
       </c>
       <c r="F35">
-        <v>-1.737060083161182</v>
+        <v>-1.897574491536447</v>
       </c>
       <c r="G35">
-        <v>-13.11970636498221</v>
+        <v>-13.89097078035729</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>5.527290502577504</v>
       </c>
       <c r="E36">
-        <v>-35.90630418284392</v>
+        <v>-37.23023978677841</v>
       </c>
       <c r="F36">
-        <v>-1.746244192556019</v>
+        <v>-1.937327014829393</v>
       </c>
       <c r="G36">
-        <v>-13.09444028142649</v>
+        <v>-13.70137252677769</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>5.097532788503728</v>
       </c>
       <c r="E37">
-        <v>-35.65899968881104</v>
+        <v>-37.17572375243707</v>
       </c>
       <c r="F37">
-        <v>-1.663544961264934</v>
+        <v>-1.717559486131878</v>
       </c>
       <c r="G37">
-        <v>-12.87719897259397</v>
+        <v>-13.54907418978906</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>4.646171301585734</v>
       </c>
       <c r="E38">
-        <v>-35.10089017397271</v>
+        <v>-36.63999395614465</v>
       </c>
       <c r="F38">
-        <v>-1.686725166297472</v>
+        <v>-1.984916722120224</v>
       </c>
       <c r="G38">
-        <v>-12.9461245307216</v>
+        <v>-13.82095605274725</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>4.173584012389735</v>
       </c>
       <c r="E39">
-        <v>-34.89438270227492</v>
+        <v>-35.74564298199979</v>
       </c>
       <c r="F39">
-        <v>-1.679529138669353</v>
+        <v>-1.709969983987429</v>
       </c>
       <c r="G39">
-        <v>-13.07299787796863</v>
+        <v>-13.9417115118377</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>3.686207561629494</v>
       </c>
       <c r="E40">
-        <v>-34.41439842101692</v>
+        <v>-35.62712602450804</v>
       </c>
       <c r="F40">
-        <v>-1.695254865444099</v>
+        <v>-1.774954578369648</v>
       </c>
       <c r="G40">
-        <v>-13.20702862467156</v>
+        <v>-13.59158821560438</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>3.192884394651931</v>
       </c>
       <c r="E41">
-        <v>-33.97752294807494</v>
+        <v>-35.17133285139902</v>
       </c>
       <c r="F41">
-        <v>-1.600463955174348</v>
+        <v>-1.717597591032407</v>
       </c>
       <c r="G41">
-        <v>-13.18406337026564</v>
+        <v>-13.73838111536121</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>2.693729371183651</v>
       </c>
       <c r="E42">
-        <v>-33.05445918448445</v>
+        <v>-34.75688011750602</v>
       </c>
       <c r="F42">
-        <v>-1.539561555353126</v>
+        <v>-1.653985601436627</v>
       </c>
       <c r="G42">
-        <v>-13.06003378163684</v>
+        <v>-13.97729656583933</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>2.198797752389189</v>
       </c>
       <c r="E43">
-        <v>-32.66978795990289</v>
+        <v>-34.2503770924591</v>
       </c>
       <c r="F43">
-        <v>-1.458578701320641</v>
+        <v>-1.641167444245708</v>
       </c>
       <c r="G43">
-        <v>-13.29495340364906</v>
+        <v>-14.17633980584247</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>1.711822166479999</v>
       </c>
       <c r="E44">
-        <v>-32.57097665705552</v>
+        <v>-33.6291157433468</v>
       </c>
       <c r="F44">
-        <v>-1.536008687562519</v>
+        <v>-1.58803678739755</v>
       </c>
       <c r="G44">
-        <v>-13.41459320889279</v>
+        <v>-13.69382779349369</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>1.231924563604942</v>
       </c>
       <c r="E45">
-        <v>-31.56760719965001</v>
+        <v>-33.1015439929792</v>
       </c>
       <c r="F45">
-        <v>-1.506394552912437</v>
+        <v>-1.692655448534114</v>
       </c>
       <c r="G45">
-        <v>-13.12259316069245</v>
+        <v>-14.07797025568856</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.7673854030325292</v>
       </c>
       <c r="E46">
-        <v>-31.26195558226529</v>
+        <v>-33.04586640505489</v>
       </c>
       <c r="F46">
-        <v>-1.381477576937674</v>
+        <v>-1.522924624435301</v>
       </c>
       <c r="G46">
-        <v>-13.38722161837409</v>
+        <v>-14.11410651552248</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>0.3155697503241013</v>
       </c>
       <c r="E47">
-        <v>-31.03412352646539</v>
+        <v>-32.32962937057972</v>
       </c>
       <c r="F47">
-        <v>-1.457510107371029</v>
+        <v>-1.647322214048508</v>
       </c>
       <c r="G47">
-        <v>-13.02760367753414</v>
+        <v>-14.4635428735564</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.1222187791619881</v>
       </c>
       <c r="E48">
-        <v>-30.58016212109247</v>
+        <v>-31.55994728586603</v>
       </c>
       <c r="F48">
-        <v>-1.376096502289089</v>
+        <v>-1.666551934937096</v>
       </c>
       <c r="G48">
-        <v>-13.30590137774743</v>
+        <v>-14.25726278100441</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.5416844795588911</v>
       </c>
       <c r="E49">
-        <v>-30.38981224465405</v>
+        <v>-31.45169185047567</v>
       </c>
       <c r="F49">
-        <v>-1.325640643784571</v>
+        <v>-1.540071829673251</v>
       </c>
       <c r="G49">
-        <v>-13.13966895458401</v>
+        <v>-14.11038049651803</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.9467214988844387</v>
       </c>
       <c r="E50">
-        <v>-29.53528014245864</v>
+        <v>-31.41392890572571</v>
       </c>
       <c r="F50">
-        <v>-1.364737928461902</v>
+        <v>-1.385993836017737</v>
       </c>
       <c r="G50">
-        <v>-13.29762170335372</v>
+        <v>-14.22027405569414</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.331818961195051</v>
       </c>
       <c r="E51">
-        <v>-29.26074140574362</v>
+        <v>-30.37509923260313</v>
       </c>
       <c r="F51">
-        <v>-1.198693339305546</v>
+        <v>-1.616107673576217</v>
       </c>
       <c r="G51">
-        <v>-13.45298891605725</v>
+        <v>-14.2399718016528</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.693850299977206</v>
       </c>
       <c r="E52">
-        <v>-28.56962834506301</v>
+        <v>-30.55394678506206</v>
       </c>
       <c r="F52">
-        <v>-1.453126387075415</v>
+        <v>-1.547734228149146</v>
       </c>
       <c r="G52">
-        <v>-13.16905004624504</v>
+        <v>-14.65907693528792</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.031113799674996</v>
       </c>
       <c r="E53">
-        <v>-28.06309588493504</v>
+        <v>-30.14112656604883</v>
       </c>
       <c r="F53">
-        <v>-1.333871302298786</v>
+        <v>-1.357564266753658</v>
       </c>
       <c r="G53">
-        <v>-13.52139802908075</v>
+        <v>-14.56574934599032</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.334257627115663</v>
       </c>
       <c r="E54">
-        <v>-27.84402642633998</v>
+        <v>-29.39354796296657</v>
       </c>
       <c r="F54">
-        <v>-1.338053729315521</v>
+        <v>-1.428690377060232</v>
       </c>
       <c r="G54">
-        <v>-13.20509526607663</v>
+        <v>-14.44834084844007</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.599501810372094</v>
       </c>
       <c r="E55">
-        <v>-27.68840088859238</v>
+        <v>-28.81213265664777</v>
       </c>
       <c r="F55">
-        <v>-1.341318325249954</v>
+        <v>-1.620606536940821</v>
       </c>
       <c r="G55">
-        <v>-13.61114195283209</v>
+        <v>-14.58250732751011</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.820940447952921</v>
       </c>
       <c r="E56">
-        <v>-26.90205854800447</v>
+        <v>-29.31362039673119</v>
       </c>
       <c r="F56">
-        <v>-1.272987126560426</v>
+        <v>-1.319700421139095</v>
       </c>
       <c r="G56">
-        <v>-13.53243538790868</v>
+        <v>-14.39325502593936</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.991487700699965</v>
       </c>
       <c r="E57">
-        <v>-26.13287006695762</v>
+        <v>-28.26288310120545</v>
       </c>
       <c r="F57">
-        <v>-1.158977264178324</v>
+        <v>-1.556206769944979</v>
       </c>
       <c r="G57">
-        <v>-13.78803267735919</v>
+        <v>-14.66980806865346</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.10875929644141</v>
       </c>
       <c r="E58">
-        <v>-26.41992550582983</v>
+        <v>-27.77805561699624</v>
       </c>
       <c r="F58">
-        <v>-1.311804423055611</v>
+        <v>-1.541157819338321</v>
       </c>
       <c r="G58">
-        <v>-13.3431417045187</v>
+        <v>-14.75573658867079</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.169641545172358</v>
       </c>
       <c r="E59">
-        <v>-26.11134170152515</v>
+        <v>-27.63209384278101</v>
       </c>
       <c r="F59">
-        <v>-1.363129238965665</v>
+        <v>-1.513744656877477</v>
       </c>
       <c r="G59">
-        <v>-13.88462777510405</v>
+        <v>-14.71401212796658</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.173754038025739</v>
       </c>
       <c r="E60">
-        <v>-25.84611350736991</v>
+        <v>-27.36785738443345</v>
       </c>
       <c r="F60">
-        <v>-1.438108914430062</v>
+        <v>-1.553371268325197</v>
       </c>
       <c r="G60">
-        <v>-13.68349061504732</v>
+        <v>-15.01690718153666</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.123428859450288</v>
       </c>
       <c r="E61">
-        <v>-25.72922000780991</v>
+        <v>-27.47128773076864</v>
       </c>
       <c r="F61">
-        <v>-1.505642395310695</v>
+        <v>-1.514653375918348</v>
       </c>
       <c r="G61">
-        <v>-13.62037340906834</v>
+        <v>-14.78645514072968</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.022352446425575</v>
       </c>
       <c r="E62">
-        <v>-25.01499361579415</v>
+        <v>-27.15290430871136</v>
       </c>
       <c r="F62">
-        <v>-1.514788399805004</v>
+        <v>-1.660085698990843</v>
       </c>
       <c r="G62">
-        <v>-13.75370563066249</v>
+        <v>-14.87508837645259</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.875288436270331</v>
       </c>
       <c r="E63">
-        <v>-25.25297851031925</v>
+        <v>-26.895877180984</v>
       </c>
       <c r="F63">
-        <v>-1.564399323558666</v>
+        <v>-1.62410970268726</v>
       </c>
       <c r="G63">
-        <v>-13.85632095547051</v>
+        <v>-14.69367379144607</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.688941481749314</v>
       </c>
       <c r="E64">
-        <v>-25.27621411045261</v>
+        <v>-26.59971045240835</v>
       </c>
       <c r="F64">
-        <v>-1.572663116768994</v>
+        <v>-1.460179935510252</v>
       </c>
       <c r="G64">
-        <v>-13.79293725057562</v>
+        <v>-14.94507165388001</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.470595387961626</v>
       </c>
       <c r="E65">
-        <v>-24.99381394286027</v>
+        <v>-26.75644999476184</v>
       </c>
       <c r="F65">
-        <v>-1.705266513874334</v>
+        <v>-1.639775787009005</v>
       </c>
       <c r="G65">
-        <v>-13.71001305063519</v>
+        <v>-14.8659297522182</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.226073382686088</v>
       </c>
       <c r="E66">
-        <v>-24.5553489755416</v>
+        <v>-26.42523740584083</v>
       </c>
       <c r="F66">
-        <v>-1.61267906089603</v>
+        <v>-1.857387075357032</v>
       </c>
       <c r="G66">
-        <v>-13.85700623839714</v>
+        <v>-15.23552733258628</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.96458763584252</v>
       </c>
       <c r="E67">
-        <v>-24.92562418125278</v>
+        <v>-26.8645265554289</v>
       </c>
       <c r="F67">
-        <v>-1.90386594196071</v>
+        <v>-2.043855062829409</v>
       </c>
       <c r="G67">
-        <v>-13.83397477308043</v>
+        <v>-15.20788262206059</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.692705392727551</v>
       </c>
       <c r="E68">
-        <v>-25.01252559745997</v>
+        <v>-26.6129607673548</v>
       </c>
       <c r="F68">
-        <v>-1.757283844933129</v>
+        <v>-2.120061550417352</v>
       </c>
       <c r="G68">
-        <v>-13.85619846528556</v>
+        <v>-14.57423924002578</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.415982783438507</v>
       </c>
       <c r="E69">
-        <v>-24.24046606389225</v>
+        <v>-26.42278750140268</v>
       </c>
       <c r="F69">
-        <v>-2.033768861332923</v>
+        <v>-2.111943549869917</v>
       </c>
       <c r="G69">
-        <v>-13.56607053058768</v>
+        <v>-14.94487964223874</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.143039339999516</v>
       </c>
       <c r="E70">
-        <v>-24.41472627218142</v>
+        <v>-26.19274555028703</v>
       </c>
       <c r="F70">
-        <v>-2.028468138322408</v>
+        <v>-2.286644578385527</v>
       </c>
       <c r="G70">
-        <v>-13.64996968618943</v>
+        <v>-14.71808244370711</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.8768494026965242</v>
       </c>
       <c r="E71">
-        <v>-24.26464811509321</v>
+        <v>-26.05409726159419</v>
       </c>
       <c r="F71">
-        <v>-2.158028113589862</v>
+        <v>-2.382188474624423</v>
       </c>
       <c r="G71">
-        <v>-13.66715141753825</v>
+        <v>-14.41330203445242</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.6225276681276468</v>
       </c>
       <c r="E72">
-        <v>-24.6591415997974</v>
+        <v>-26.33690499184721</v>
       </c>
       <c r="F72">
-        <v>-2.437631933261196</v>
+        <v>-2.251657652760887</v>
       </c>
       <c r="G72">
-        <v>-13.43046396420805</v>
+        <v>-14.56515179252048</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.384558688820047</v>
       </c>
       <c r="E73">
-        <v>-24.54602484755981</v>
+        <v>-26.17499393217697</v>
       </c>
       <c r="F73">
-        <v>-2.291246987675482</v>
+        <v>-2.457351219284838</v>
       </c>
       <c r="G73">
-        <v>-13.45616041868388</v>
+        <v>-14.82229179619229</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.1626982285969988</v>
       </c>
       <c r="E74">
-        <v>-24.40873962954327</v>
+        <v>-26.2826991579754</v>
       </c>
       <c r="F74">
-        <v>-2.413745959201473</v>
+        <v>-2.555214544251572</v>
       </c>
       <c r="G74">
-        <v>-13.10231275871887</v>
+        <v>-14.40931448235037</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.0389608828098048</v>
       </c>
       <c r="E75">
-        <v>-24.53185525238981</v>
+        <v>-26.61328228900934</v>
       </c>
       <c r="F75">
-        <v>-2.537464287544384</v>
+        <v>-2.5077606892148</v>
       </c>
       <c r="G75">
-        <v>-13.24324268232565</v>
+        <v>-14.16576095757173</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.2203923896069925</v>
       </c>
       <c r="E76">
-        <v>-24.82207609459338</v>
+        <v>-26.16322442823103</v>
       </c>
       <c r="F76">
-        <v>-2.722251517556481</v>
+        <v>-2.741827496019439</v>
       </c>
       <c r="G76">
-        <v>-12.91155912474607</v>
+        <v>-14.06365545677676</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.3822733868330738</v>
       </c>
       <c r="E77">
-        <v>-25.18387852543621</v>
+        <v>-26.73583638107893</v>
       </c>
       <c r="F77">
-        <v>-2.88584413920055</v>
+        <v>-2.952065486115148</v>
       </c>
       <c r="G77">
-        <v>-13.20267856783296</v>
+        <v>-14.09238106042101</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.522804627364144</v>
       </c>
       <c r="E78">
-        <v>-25.42472541553416</v>
+        <v>-27.01535643920238</v>
       </c>
       <c r="F78">
-        <v>-2.903789062247395</v>
+        <v>-2.748229119308274</v>
       </c>
       <c r="G78">
-        <v>-12.70105808663151</v>
+        <v>-13.80291689010376</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.6438296216840816</v>
       </c>
       <c r="E79">
-        <v>-24.95632270655077</v>
+        <v>-27.39820268875884</v>
       </c>
       <c r="F79">
-        <v>-2.792453169841531</v>
+        <v>-3.013993404781036</v>
       </c>
       <c r="G79">
-        <v>-13.0410709767879</v>
+        <v>-14.00163073082574</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.7449354598209736</v>
       </c>
       <c r="E80">
-        <v>-26.27202554473932</v>
+        <v>-27.61181080770066</v>
       </c>
       <c r="F80">
-        <v>-2.939123073813808</v>
+        <v>-2.895626329860209</v>
       </c>
       <c r="G80">
-        <v>-12.40672079328045</v>
+        <v>-13.76464367312424</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.8256355751612126</v>
       </c>
       <c r="E81">
-        <v>-26.27119683399592</v>
+        <v>-28.15403217148307</v>
       </c>
       <c r="F81">
-        <v>-2.968424085585633</v>
+        <v>-3.059915608490032</v>
       </c>
       <c r="G81">
-        <v>-12.23578408490572</v>
+        <v>-13.4841080441264</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.8871907600727734</v>
       </c>
       <c r="E82">
-        <v>-26.51382341437888</v>
+        <v>-27.97336870094706</v>
       </c>
       <c r="F82">
-        <v>-2.796899017692356</v>
+        <v>-3.033614943451148</v>
       </c>
       <c r="G82">
-        <v>-12.26868097592946</v>
+        <v>-13.66608873242014</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.9289402122558114</v>
       </c>
       <c r="E83">
-        <v>-26.94570850896441</v>
+        <v>-28.75557654476597</v>
       </c>
       <c r="F83">
-        <v>-2.932971617480619</v>
+        <v>-3.071163181085244</v>
       </c>
       <c r="G83">
-        <v>-12.02118790195908</v>
+        <v>-13.53427605122852</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.9514332656074362</v>
       </c>
       <c r="E84">
-        <v>-27.88143615011735</v>
+        <v>-29.39044595827132</v>
       </c>
       <c r="F84">
-        <v>-3.349524449652379</v>
+        <v>-3.034461534936809</v>
       </c>
       <c r="G84">
-        <v>-12.07909927507755</v>
+        <v>-13.41593397983619</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.9552067976464689</v>
       </c>
       <c r="E85">
-        <v>-28.39900902987602</v>
+        <v>-29.97201523270638</v>
       </c>
       <c r="F85">
-        <v>-3.052828925359083</v>
+        <v>-3.074407067834607</v>
       </c>
       <c r="G85">
-        <v>-11.97417815530143</v>
+        <v>-13.09568835709479</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.9407897643911713</v>
       </c>
       <c r="E86">
-        <v>-28.94913710927583</v>
+        <v>-31.11485716107414</v>
       </c>
       <c r="F86">
-        <v>-3.168192340077359</v>
+        <v>-3.291906526583256</v>
       </c>
       <c r="G86">
-        <v>-11.68939840692225</v>
+        <v>-13.47276280456332</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.9090201619100863</v>
       </c>
       <c r="E87">
-        <v>-30.50498265985413</v>
+        <v>-31.41776905168421</v>
       </c>
       <c r="F87">
-        <v>-3.156892580335771</v>
+        <v>-3.350026440298475</v>
       </c>
       <c r="G87">
-        <v>-12.14709456990864</v>
+        <v>-13.2488275726504</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.8607363131082399</v>
       </c>
       <c r="E88">
-        <v>-31.03547527595668</v>
+        <v>-32.32732664154683</v>
       </c>
       <c r="F88">
-        <v>-3.172981132032942</v>
+        <v>-3.166940676931728</v>
       </c>
       <c r="G88">
-        <v>-11.79169095354019</v>
+        <v>-12.99694140474941</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.7968334992333522</v>
       </c>
       <c r="E89">
-        <v>-32.09754054921261</v>
+        <v>-33.48909532702964</v>
       </c>
       <c r="F89">
-        <v>-3.210954322144675</v>
+        <v>-3.334944354995705</v>
       </c>
       <c r="G89">
-        <v>-11.66138126002339</v>
+        <v>-13.23049046090838</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.717489730985463</v>
       </c>
       <c r="E90">
-        <v>-33.17754310801293</v>
+        <v>-34.46340556672793</v>
       </c>
       <c r="F90">
-        <v>-3.186281399052291</v>
+        <v>-3.517123056056386</v>
       </c>
       <c r="G90">
-        <v>-11.85098613469407</v>
+        <v>-13.53481235960588</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.6245692577875325</v>
       </c>
       <c r="E91">
-        <v>-34.27370552630961</v>
+        <v>-35.50988836092347</v>
       </c>
       <c r="F91">
-        <v>-3.384049146266257</v>
+        <v>-3.377671545632103</v>
       </c>
       <c r="G91">
-        <v>-11.91245634426726</v>
+        <v>-13.13823879891105</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.5193829553127135</v>
       </c>
       <c r="E92">
-        <v>-35.41525910382219</v>
+        <v>-36.97324888684312</v>
       </c>
       <c r="F92">
-        <v>-3.601535351136461</v>
+        <v>-3.670803433358556</v>
       </c>
       <c r="G92">
-        <v>-11.83972034822393</v>
+        <v>-13.32419545239745</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.4032845826762284</v>
       </c>
       <c r="E93">
-        <v>-36.25045688624185</v>
+        <v>-37.7497712315454</v>
       </c>
       <c r="F93">
-        <v>-3.722469536638564</v>
+        <v>-3.736132628580339</v>
       </c>
       <c r="G93">
-        <v>-12.19949057415869</v>
+        <v>-13.63177823845113</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.2794139110994455</v>
       </c>
       <c r="E94">
-        <v>-37.99364993499148</v>
+        <v>-39.00570953401771</v>
       </c>
       <c r="F94">
-        <v>-3.543430348034493</v>
+        <v>-3.764057722096113</v>
       </c>
       <c r="G94">
-        <v>-12.4658272733386</v>
+        <v>-13.37697879047559</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.1495519385162669</v>
       </c>
       <c r="E95">
-        <v>-39.55740672966118</v>
+        <v>-40.29849376525344</v>
       </c>
       <c r="F95">
-        <v>-3.699433467534112</v>
+        <v>-3.846278157028381</v>
       </c>
       <c r="G95">
-        <v>-12.41514613167789</v>
+        <v>-13.26340059411427</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.01862113387708213</v>
       </c>
       <c r="E96">
-        <v>-40.87471491188545</v>
+        <v>-42.42288696325775</v>
       </c>
       <c r="F96">
-        <v>-3.848918992308505</v>
+        <v>-4.029685326947414</v>
       </c>
       <c r="G96">
-        <v>-12.55300717956976</v>
+        <v>-13.45377351535006</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.1086770530286829</v>
       </c>
       <c r="E97">
-        <v>-42.45172202150159</v>
+        <v>-43.52223063454483</v>
       </c>
       <c r="F97">
-        <v>-3.847873592646172</v>
+        <v>-4.1524195548158</v>
       </c>
       <c r="G97">
-        <v>-13.04970487955432</v>
+        <v>-14.21546548829835</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.2263034272575787</v>
       </c>
       <c r="E98">
-        <v>-43.8997649840903</v>
+        <v>-45.04030644766215</v>
       </c>
       <c r="F98">
-        <v>-4.028020308467786</v>
+        <v>-4.00229618714125</v>
       </c>
       <c r="G98">
-        <v>-13.09839969389146</v>
+        <v>-14.00548751637899</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.3286906576135775</v>
       </c>
       <c r="E99">
-        <v>-45.68997717846157</v>
+        <v>-46.62234242766381</v>
       </c>
       <c r="F99">
-        <v>-4.175154926553034</v>
+        <v>-4.201623750174687</v>
       </c>
       <c r="G99">
-        <v>-13.09882344372048</v>
+        <v>-14.44359683668229</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.4073076072404965</v>
       </c>
       <c r="E100">
-        <v>-47.17872659390522</v>
+        <v>-48.43170327437652</v>
       </c>
       <c r="F100">
-        <v>-4.292302644656941</v>
+        <v>-4.415560400723896</v>
       </c>
       <c r="G100">
-        <v>-13.54101135612817</v>
+        <v>-14.8837338661284</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.4612201819204054</v>
       </c>
       <c r="E101">
-        <v>-49.25925925690824</v>
+        <v>-50.02937154665266</v>
       </c>
       <c r="F101">
-        <v>-4.309326423151873</v>
+        <v>-4.467580216884899</v>
       </c>
       <c r="G101">
-        <v>-13.88379517290092</v>
+        <v>-15.07770203981983</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.4768167739592647</v>
       </c>
       <c r="E102">
-        <v>-51.26533022180313</v>
+        <v>-51.95709877909636</v>
       </c>
       <c r="F102">
-        <v>-4.403252517853101</v>
+        <v>-4.572950207255802</v>
       </c>
       <c r="G102">
-        <v>-14.03786299648029</v>
+        <v>-14.95849260549622</v>
       </c>
     </row>
   </sheetData>
